--- a/exports/2025vaale.xlsx
+++ b/exports/2025vaale.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
   <si>
     <t>eventKey</t>
   </si>
@@ -101,6 +101,18 @@
   </si>
   <si>
     <t>Stationary</t>
+  </si>
+  <si>
+    <t>frc9072</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Offensive</t>
+  </si>
+  <si>
+    <t>Double Shooter</t>
   </si>
 </sst>
 </file>
@@ -477,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -600,6 +612,47 @@
         <v>29</v>
       </c>
       <c r="M3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
         <v>23</v>
       </c>
     </row>
